--- a/output/pdf_financials_xlsx/NIM.xlsx
+++ b/output/pdf_financials_xlsx/NIM.xlsx
@@ -1441,7 +1441,7 @@
         <v>0.148519</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>0.069214</v>
+        <v>-1.13338</v>
       </c>
       <c r="R17" s="3" t="n">
         <v>-0</v>
@@ -1696,7 +1696,7 @@
         <v>-0.052832</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>0.601297</v>
+        <v>-0.601297</v>
       </c>
       <c r="R20" s="3" t="n">
         <v>-5.230946</v>
@@ -1879,7 +1879,7 @@
         <v>-0.052832</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>0.601297</v>
+        <v>-0.601297</v>
       </c>
       <c r="R23" s="3" t="n">
         <v>-5.230946</v>
@@ -2405,7 +2405,7 @@
         <v>-73.76124280485323</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>13.00812091346651</v>
+        <v>213.0081209134665</v>
       </c>
       <c r="R31" s="3" t="n">
         <v>-0</v>
@@ -6405,7 +6405,7 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.081404</v>
       </c>
       <c r="E92" s="3" t="n">
         <v>3.127967</v>
@@ -28704,7 +28704,11 @@
           <t>Share-based payments reserve 14 3,127,967</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr"/>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E189" t="inlineStr">
         <is>
           <t>-</t>
@@ -79889,7 +79893,7 @@
         <v>-0.052832</v>
       </c>
       <c r="T676" s="5" t="n">
-        <v>0.601297</v>
+        <v>-0.601297</v>
       </c>
       <c r="U676" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/NIM.xlsx
+++ b/output/pdf_financials_xlsx/NIM.xlsx
@@ -2567,7 +2567,7 @@
         <v>0.916286</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.895774</v>
       </c>
       <c r="Q34" s="3" t="n">
         <v>0.895774</v>
@@ -2697,7 +2697,7 @@
         <v>0.916286</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.895774</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>0.895774</v>
@@ -3477,7 +3477,7 @@
         <v>0.09392300000000001</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.907655</v>
+        <v>0.011881</v>
       </c>
       <c r="Q48" s="3" t="n">
         <v>0.011881</v>
@@ -15138,7 +15138,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -62932,7 +62932,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D516" t="inlineStr"/>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E516" t="inlineStr">
         <is>
           <t>-</t>
